--- a/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +718,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -735,7 +746,6 @@
           <t>NG_SB_CLOS_EXCEPTION AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -753,7 +763,6 @@
           <t>DIM_CLOS_APPLICATION AS B</t>
         </is>
       </c>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -771,7 +780,6 @@
           <t>DIM_CLOS_EXCEPTION AS C</t>
         </is>
       </c>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -789,7 +797,6 @@
           <t>NG_SB_CLOS_ENTRY_EXIT AS D</t>
         </is>
       </c>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -798,7 +805,6 @@
           <t>DIM_LOS_USER AS E</t>
         </is>
       </c>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -807,7 +813,6 @@
           <t>NG_SB_CLOS_CUST_INFO_LEGAL AS F</t>
         </is>
       </c>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
@@ -816,42 +821,34 @@
           <t>DIM_CLOS_CUSTOMER AS G</t>
         </is>
       </c>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -879,9 +876,8 @@
           <t>How to mapping CLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16" ht="75" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -895,9 +891,8 @@
           <t>ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1 AND A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND A.WI_NAME IS NOT NULL</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -913,19 +908,18 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK (1/2) — Driving: NG_SB_CLOS_EXCEPTION. Ngày dữ liệu. Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_BK</t>
@@ -941,17 +935,16 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(A.WI_NAME || A.EXCEPTION_CATEGORY || A.RAISED_BY || TO_CHAR(A.RAISED_DATE_TIME, 'YYYY-MM-DD HH24:MI:SS')|| A.RECID, 'MD5')</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
@@ -969,19 +962,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_APPLICATION theo phiên bản hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="75" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_SK</t>
@@ -997,19 +989,18 @@
           <t>Khóa tới ngoại lệ</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột): (1) JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM (còn phân biệt theo ACTIVITYNAME/DECISION_CODE); (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ. [CẦN REVIEW] Mặc định -1 nếu không còn dòng nào khớp</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột): (1) JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM (còn phân biệt theo ACTIVITYNAME/DECISION_CODE); (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ.</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>C.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
           <t>USER_SK</t>
@@ -1025,19 +1016,18 @@
           <t>Khóa tới người nêu lý do</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu [CẦN REVIEW] Mặc định -1</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>E.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
           <t>CUSTOMER_SK</t>
@@ -1053,17 +1043,16 @@
           <t>Khóa tới khách hàng</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER (review 2026-09-26, bổ sung vật lý — trước đây chỉ là lookup tạm để tính CHECK_FTR, chưa denormalize thành cột). Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM) [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM)</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>G.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -1081,17 +1070,16 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng CLOS</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1109,17 +1097,16 @@
           <t>Phân nhóm nội dung</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Phân nhóm nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
@@ -1137,17 +1124,16 @@
           <t>Người nêu nội dung</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Người nêu nội dung cần làm rõ. Cột USER_SK bên cạnh giữ khóa tới DIM</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_BY</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1165,17 +1151,16 @@
           <t>Thời điểm nêu nội dung</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Thời điểm nêu nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -1193,17 +1178,16 @@
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
@@ -1221,17 +1205,16 @@
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
@@ -1249,211 +1232,83 @@
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="85" customHeight="1"/>
+    </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="D31" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+    </row>
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="25" t="n"/>
       <c r="C32" s="51" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="54" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="25" t="n"/>
       <c r="C33" s="51" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="54" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="25" t="n"/>
       <c r="C34" s="51" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="54" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
       <c r="C35" s="51" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="54" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND UPPER(F.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY F.WI_NAME ORDER BY F.RECID DESC) = 1</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="25" t="n"/>
       <c r="C36" s="51" t="n"/>
-      <c r="D36" s="8" t="n"/>
+      <c r="D36" s="54" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN G.CUSTOMER_CODE = F.ID_NUMBER AND v_batch_date BETWEEN G.EFF_DATE AND NVL(G.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="51" customHeight="1"/>
-    <row r="38" ht="51" customHeight="1"/>
-    <row r="39" ht="34" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1"/>
-    <row r="41" ht="34" customHeight="1"/>
-    <row r="42" ht="17" customHeight="1"/>
-    <row r="43" ht="34" customHeight="1"/>
-    <row r="44" ht="17" customHeight="1"/>
-    <row r="45" ht="85" customHeight="1"/>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,6 +409,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +758,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng Fact ngoại lệ/nội dung cần làm rõ CLOS, driving từ NG_SB_CLOS_EXCEPTION</t>
+          <t>Bảng FACT ghi nhận từng lần một lý do (ngoại lệ) được nêu ra trên hồ sơ CLOS trong quá trình xử lý (cả Raise và Clear)</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -877,7 +880,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="75" customHeight="1">
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -886,11 +889,7 @@
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1 AND A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND A.WI_NAME IS NOT NULL</t>
-        </is>
-      </c>
+      <c r="E16" s="6" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -910,7 +909,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: NG_SB_CLOS_EXCEPTION. Ngày dữ liệu. Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
+          <t>Ngày dữ liệu. Ảnh chụp đầy đủ theo ngày (quy trình A2). Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -919,7 +918,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="105" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_BK</t>
@@ -932,12 +931,12 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ</t>
+          <t>Khóa nghiệp vụ dòng ngoại lệ</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn</t>
+          <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn. PK đổi từ composite (DAYID,WI_NAME,EXCEPTION_CATEGORY,RAISED_BY,RAISED_DATE_TIME) thành (DAYID,EXCEPTION_BK). Không có thành phần DATASOURCE trong công thức hash (cột DATASOURCE không có trong thiết kế bảng).</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -946,7 +945,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -959,12 +958,12 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+          <t>Khóa tới DIM_CLOS_APPLICATION theo phiên bản hiệu lực tại DAYID. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
@@ -973,337 +972,456 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="75" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_SK</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột): (1) JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM (còn phân biệt theo ACTIVITYNAME/DECISION_CODE); (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ.</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>C.DIMENSION_KEY</t>
-        </is>
-      </c>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="55" t="inlineStr">
+        <is>
+          <t>Filter sau khi hash: ROW_NUMBER() OVER (PARTITION BY WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME, EXCEPTION_NAME, EXCEPTION_REMARKS ORDER BY RECID DESC) = 1; Filter từ nguồn: A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND A.WI_NAME IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng CLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — bước (1) EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM_CLOS_EXCEPTION (vì DIM còn phân biệt theo ACTIVITYNAME/DECISION_CODE); bước (2) EXISTS lọc còn đúng 1 dòng — chỉ giữ tổ hợp ACTIVITYNAME/DECISION_CODE đã thực sự xảy ra trong lịch sử xử lý hồ sơ trên NG_SB_CLOS_ENTRY_EXIT. Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_CLOS_EXCEPTION_REASON→DIM_CLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>WORKSTEP_CODE</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_CLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_CLOS_EXCEPTION</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>C.ACTIVITYNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>DECISION_CODE</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Mã quyết định ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_CLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>C.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>USER_SK</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Khóa người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>E.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>USERNAME</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(150)</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Tên tài khoản người nêu</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>CUSTOMER_SK</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới khách hàng</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM)</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Khóa khách hàng</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM). Mặc định -1 nếu không khớp</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>G.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>WI_NAME</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CODE</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng CLOS</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Mã khách hàng</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Mã khách hàng (BK của DIM_CLOS_CUSTOMER)</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>F.ID_NUMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Phân nhóm nội dung</t>
         </is>
       </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>RAISED_BY</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USER_SK bên cạnh giữ khóa tới DIM</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm nêu nội dung</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>Thời điểm nêu nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu lý do</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_DATE_TIME</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_NAME</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Tên nội dung ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="D27" s="54" t="inlineStr">
-        <is>
-          <t>Tên nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>RCTYPE</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="55" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="56" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="51" t="n"/>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="51" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="51" t="n"/>
-      <c r="D33" s="54" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="51" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="51" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="8" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="25" t="n"/>
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="51" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="54" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="25" t="n"/>
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="51" t="n"/>
+      <c r="D40" s="54" t="n"/>
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND UPPER(F.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY F.WI_NAME ORDER BY F.RECID DESC) = 1</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="51" t="n"/>
-      <c r="D36" s="54" t="n"/>
-      <c r="E36" s="8" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="25" t="n"/>
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="51" t="n"/>
+      <c r="D41" s="54" t="n"/>
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN G.CUSTOMER_CODE = F.ID_NUMBER AND v_batch_date BETWEEN G.EFF_DATE AND NVL(G.EXP_DATE, v_batch_date)</t>
         </is>

--- a/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,9 +409,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -880,7 +877,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -889,7 +886,11 @@
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND A.WI_NAME IS NOT NULL AND ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -972,456 +973,445 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="55" t="inlineStr">
-        <is>
-          <t>Filter sau khi hash: ROW_NUMBER() OVER (PARTITION BY WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME, EXCEPTION_NAME, EXCEPTION_REMARKS ORDER BY RECID DESC) = 1; Filter từ nguồn: A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND A.WI_NAME IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng CLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="150" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>EXCEPTION_SK</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Khóa ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — bước (1) EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM_CLOS_EXCEPTION (vì DIM còn phân biệt theo ACTIVITYNAME/DECISION_CODE); bước (2) EXISTS lọc còn đúng 1 dòng — chỉ giữ tổ hợp ACTIVITYNAME/DECISION_CODE đã thực sự xảy ra trong lịch sử xử lý hồ sơ trên NG_SB_CLOS_ENTRY_EXIT. Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_CLOS_EXCEPTION_REASON→DIM_CLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>WORKSTEP_CODE</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_CLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_CLOS_EXCEPTION</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>C.ACTIVITYNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>DECISION_CODE</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã quyết định ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_CLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>C.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>USER_SK</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Khóa người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>E.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>USERNAME</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(150)</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Tên tài khoản người nêu</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>CUSTOMER_SK</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Khóa khách hàng</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM). Mặc định -1 nếu không khớp</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>G.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CODE</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng CLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_SK</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — bước (1) EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM_CLOS_EXCEPTION (vì DIM còn phân biệt theo ACTIVITYNAME/DECISION_CODE); bước (2) EXISTS lọc còn đúng 1 dòng — chỉ giữ tổ hợp ACTIVITYNAME/DECISION_CODE đã thực sự xảy ra trong lịch sử xử lý hồ sơ trên NG_SB_CLOS_ENTRY_EXIT. Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_CLOS_EXCEPTION_REASON→DIM_CLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>C.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>WORKSTEP_CODE</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Mã bước xử lý ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_CLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_CLOS_EXCEPTION</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>C.ACTIVITYNAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>DECISION_CODE</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Mã quyết định ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_CLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>C.DECISION_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>USER_SK</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Khóa người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>E.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>USERNAME</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(150)</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Tên tài khoản người nêu</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>CUSTOMER_SK</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Khóa khách hàng</t>
+          <t>Mã khách hàng</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM). Mặc định -1 nếu không khớp</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã khách hàng (BK của DIM_CLOS_CUSTOMER)</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>G.DIMENSION_KEY</t>
+          <t>F.ID_NUMBER</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_CODE</t>
+          <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>A.EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_BY</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Mã khách hàng</t>
-        </is>
-      </c>
-      <c r="D28" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: Mã khách hàng (BK của DIM_CLOS_CUSTOMER)</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>F.ID_NUMBER</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_DATE_TIME</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu lý do</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_DATE_TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_NAME</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>RAISED_BY</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>RAISED_DATE_TIME</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm nêu lý do</t>
+          <t>Tên nội dung ngoại lệ</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_DATE_TIME</t>
+          <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_NAME</t>
+          <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(4000)</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Tên nội dung ngoại lệ</t>
+          <t>Ghi chú ngoại lệ</t>
         </is>
       </c>
       <c r="D32" s="54" t="inlineStr">
         <is>
-          <t>Tên nội dung cần làm rõ</t>
+          <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_NAME</t>
+          <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_REMARKS</t>
+          <t>RCTYPE</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(4000)</t>
+          <t>VARCHAR2(20)</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Ghi chú ngoại lệ</t>
+          <t>Loại ghi nhận</t>
         </is>
       </c>
       <c r="D33" s="54" t="inlineStr">
         <is>
-          <t>Ghi chú của nội dung cần làm rõ</t>
+          <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
       <c r="E33" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>RCTYPE</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(20)</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận, Raise hay Clear</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="56" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="51" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="25" t="n"/>
       <c r="C37" s="51" t="n"/>
       <c r="D37" s="54" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="25" t="n"/>
       <c r="C38" s="51" t="n"/>
       <c r="D38" s="54" t="n"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+          <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="25" t="n"/>
       <c r="C39" s="51" t="n"/>
       <c r="D39" s="54" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND UPPER(F.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY F.WI_NAME ORDER BY F.RECID DESC) = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="25" t="n"/>
       <c r="C40" s="51" t="n"/>
       <c r="D40" s="54" t="n"/>
       <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND UPPER(F.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY F.WI_NAME ORDER BY F.RECID DESC) = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="25" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="51" t="n"/>
-      <c r="D41" s="54" t="n"/>
-      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN G.CUSTOMER_CODE = F.ID_NUMBER AND v_batch_date BETWEEN G.EFF_DATE AND NVL(G.EXP_DATE, v_batch_date)</t>
         </is>

--- a/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -413,6 +413,9 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -718,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -777,7 +780,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>DIM_CLOS_EXCEPTION AS C</t>
+          <t>DIM_LOS_USER AS C</t>
         </is>
       </c>
     </row>
@@ -794,7 +797,7 @@
       </c>
       <c r="E4" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_CLOS_ENTRY_EXIT AS D</t>
+          <t>NG_SB_CLOS_CUST_INFO_LEGAL AS D</t>
         </is>
       </c>
     </row>
@@ -802,25 +805,17 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>DIM_LOS_USER AS E</t>
+          <t>DIM_CLOS_CUSTOMER AS E</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
-      <c r="E6" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_CLOS_CUST_INFO_LEGAL AS F</t>
-        </is>
-      </c>
+      <c r="E6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
-      <c r="E7" s="52" t="inlineStr">
-        <is>
-          <t>DIM_CLOS_CUSTOMER AS G</t>
-        </is>
-      </c>
+      <c r="E7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
@@ -1000,10 +995,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="150" customHeight="1">
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_SK</t>
+          <t>USER_SK</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -1013,12 +1008,12 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa ngoại lệ</t>
+          <t>Khóa người nêu lý do</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — bước (1) EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM_CLOS_EXCEPTION (vì DIM còn phân biệt theo ACTIVITYNAME/DECISION_CODE); bước (2) EXISTS lọc còn đúng 1 dòng — chỉ giữ tổ hợp ACTIVITYNAME/DECISION_CODE đã thực sự xảy ra trong lịch sử xử lý hồ sơ trên NG_SB_CLOS_ENTRY_EXIT. Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_CLOS_EXCEPTION_REASON→DIM_CLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
@@ -1027,172 +1022,172 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>WORKSTEP_CODE</t>
+          <t>USERNAME</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(150)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Mã bước xử lý ngoại lệ</t>
+          <t>Tên tài khoản người nêu</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_CLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_CLOS_EXCEPTION</t>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>C.ACTIVITYNAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>DECISION_CODE</t>
+          <t>CUSTOMER_SK</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Mã quyết định ngoại lệ</t>
+          <t>Khóa khách hàng</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_CLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM). Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>C.DECISION_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>E.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Khóa người nêu lý do</t>
+          <t>Mã khách hàng</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã khách hàng (BK của DIM_CLOS_CUSTOMER)</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>E.DIMENSION_KEY</t>
+          <t>D.ID_NUMBER</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>USERNAME</t>
+          <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(150)</t>
+          <t>VARCHAR2(500)</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Tên tài khoản người nêu</t>
+          <t>Phân nhóm nội dung</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
+          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_BY</t>
+          <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_SK</t>
+          <t>RAISED_BY</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Khóa khách hàng</t>
+          <t>Người nêu lý do</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER. Để PDTD_DTM tra CUST_GROUP phân nhóm whitelist khi tính lại CHECK_FTR (đã chuyển hẳn sang PDTD_DTM). Mặc định -1 nếu không khớp</t>
+          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>G.DIMENSION_KEY</t>
+          <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_CODE</t>
+          <t>RAISED_DATE_TIME</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Mã khách hàng</t>
+          <t>Thời điểm nêu lý do</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: Mã khách hàng (BK của DIM_CLOS_CUSTOMER)</t>
+          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>F.ID_NUMBER</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>A.RAISED_DATE_TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_CATEGORY</t>
+          <t>EXCEPTION_NAME</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -1202,165 +1197,117 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung</t>
+          <t>Tên nội dung ngoại lệ</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>A.EXCEPTION_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>RAISED_BY</t>
+          <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(4000)</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Người nêu lý do</t>
+          <t>Ghi chú ngoại lệ</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t>A.EXCEPTION_REMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>RAISED_DATE_TIME</t>
+          <t>RCTYPE</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR2(20)</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm nêu lý do</t>
+          <t>Loại ghi nhận</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_DATE_TIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_NAME</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(500)</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Tên nội dung ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Tên nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(4000)</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Ghi chú của nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>RCTYPE</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(20)</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận, Raise hay Clear</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="55" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="51" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="51" t="n"/>
+      <c r="D34" s="54" t="n"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="51" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D.WI_NAME = A.WI_NAME AND UPPER(D.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY D.WI_NAME ORDER BY D.RECID DESC) = 1</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="25" t="n"/>
@@ -1369,51 +1316,19 @@
       <c r="D36" s="54" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="51" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="51" t="n"/>
-      <c r="D38" s="54" t="n"/>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="25" t="n"/>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="51" t="n"/>
-      <c r="D39" s="54" t="n"/>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND UPPER(F.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY F.WI_NAME ORDER BY F.RECID DESC) = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="51" t="n"/>
-      <c r="D40" s="54" t="n"/>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN G.CUSTOMER_CODE = F.ID_NUMBER AND v_batch_date BETWEEN G.EFF_DATE AND NVL(G.EXP_DATE, v_batch_date)</t>
+          <t>LEFT JOIN E.CUSTOMER_CODE = D.ID_NUMBER AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>Chú ý:</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="inlineStr">
+        <is>
+          <t>1. SRS BC7 cập nhật 2026-10-28: bỏ EXCEPTION_SK/WORKSTEP_CODE/DECISION_CODE — FCT không còn lookup sang DIM_CLOS_EXCEPTION ở tầng SB_DWH (thuật toán mới không còn đủ khóa EXCEPTION_NAME để lookup DIM 1:1 ổn định). Việc tính WORKSTEP_CODE (thay ACTIVITYNAME) chuyển hẳn xuống PDTD_DTM.</t>
         </is>
       </c>
     </row>
